--- a/planning/planning_betpulse.xlsx
+++ b/planning/planning_betpulse.xlsx
@@ -703,7 +703,7 @@
     <row r="27">
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>7. La colonne avancement se calcule seule. Pour une nouvelle ligne, recopier la formule de la ligne du dessus.</t>
+          <t>7. La colonne avancement se calcule seule. Pour une nouvelle ligne, recopier la formule de la ligne du dessus (dans Google Sheets, elle s'étend toute seule).</t>
         </is>
       </c>
     </row>

--- a/planning/planning_betpulse.xlsx
+++ b/planning/planning_betpulse.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Référentiels" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Épreuves'!$A$1:$T$752</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Épreuves'!$A$1:$T$799</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T752"/>
+  <dimension ref="A1:T799"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -22477,7 +22477,7 @@
         <v>46318</v>
       </c>
       <c r="I256" s="10" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="J256" s="11" t="n"/>
       <c r="K256" s="9" t="inlineStr">
@@ -22508,7 +22508,7 @@
       </c>
       <c r="Q256" s="9" t="inlineStr">
         <is>
-          <t>https://www.lnh.fr/daikin-starligue/accueil</t>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
         </is>
       </c>
       <c r="R256" s="10" t="n">
@@ -22516,7 +22516,7 @@
       </c>
       <c r="S256" s="9" t="inlineStr">
         <is>
-          <t>Matchs vérifiés ven. 23 et sam. 24 oct. ; dimanche éventuel à confirmer</t>
+          <t>Plage de la journée selon le calendrier provisoire LNH</t>
         </is>
       </c>
       <c r="T256" s="9">
@@ -22593,7 +22593,7 @@
       </c>
       <c r="Q257" s="9" t="inlineStr">
         <is>
-          <t>https://www.teamchambe.com/equipe-premiere/calendrier-resultats/</t>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
         </is>
       </c>
       <c r="R257" s="10" t="n">
@@ -22601,7 +22601,7 @@
       </c>
       <c r="S257" s="9" t="inlineStr">
         <is>
-          <t>Chambéry ven. 30/10, Paris – Montpellier le 1er nov.</t>
+          <t>Plage de la journée selon le calendrier provisoire LNH</t>
         </is>
       </c>
       <c r="T257" s="9">
@@ -22647,7 +22647,7 @@
         <v>46339</v>
       </c>
       <c r="I258" s="10" t="n">
-        <v>46339</v>
+        <v>46341</v>
       </c>
       <c r="J258" s="11" t="n"/>
       <c r="K258" s="9" t="inlineStr">
@@ -22678,7 +22678,7 @@
       </c>
       <c r="Q258" s="9" t="inlineStr">
         <is>
-          <t>https://www.teamchambe.com/equipe-premiere/calendrier-resultats/</t>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
         </is>
       </c>
       <c r="R258" s="10" t="n">
@@ -22686,7 +22686,7 @@
       </c>
       <c r="S258" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Chambéry (calendrier club) ; plage complète de la journée à confirmer sur lnh.fr</t>
+          <t>Plage de la journée selon le calendrier provisoire LNH</t>
         </is>
       </c>
       <c r="T258" s="9">
@@ -22732,7 +22732,7 @@
         <v>46346</v>
       </c>
       <c r="I259" s="10" t="n">
-        <v>46346</v>
+        <v>46348</v>
       </c>
       <c r="J259" s="11" t="n"/>
       <c r="K259" s="9" t="inlineStr">
@@ -22763,7 +22763,7 @@
       </c>
       <c r="Q259" s="9" t="inlineStr">
         <is>
-          <t>https://www.teamchambe.com/equipe-premiere/calendrier-resultats/</t>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
         </is>
       </c>
       <c r="R259" s="10" t="n">
@@ -22771,7 +22771,7 @@
       </c>
       <c r="S259" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Chambéry (calendrier club) ; plage complète de la journée à confirmer sur lnh.fr</t>
+          <t>Plage de la journée selon le calendrier provisoire LNH</t>
         </is>
       </c>
       <c r="T259" s="9">
@@ -22817,7 +22817,7 @@
         <v>46353</v>
       </c>
       <c r="I260" s="10" t="n">
-        <v>46353</v>
+        <v>46355</v>
       </c>
       <c r="J260" s="11" t="n"/>
       <c r="K260" s="9" t="inlineStr">
@@ -22848,7 +22848,7 @@
       </c>
       <c r="Q260" s="9" t="inlineStr">
         <is>
-          <t>https://www.teamchambe.com/equipe-premiere/calendrier-resultats/</t>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
         </is>
       </c>
       <c r="R260" s="10" t="n">
@@ -22856,7 +22856,7 @@
       </c>
       <c r="S260" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Chambéry (calendrier club) ; plage complète de la journée à confirmer sur lnh.fr</t>
+          <t>Plage de la journée selon le calendrier provisoire LNH</t>
         </is>
       </c>
       <c r="T260" s="9">
@@ -22902,7 +22902,7 @@
         <v>46360</v>
       </c>
       <c r="I261" s="10" t="n">
-        <v>46360</v>
+        <v>46362</v>
       </c>
       <c r="J261" s="11" t="n"/>
       <c r="K261" s="9" t="inlineStr">
@@ -22933,7 +22933,7 @@
       </c>
       <c r="Q261" s="9" t="inlineStr">
         <is>
-          <t>https://www.teamchambe.com/equipe-premiere/calendrier-resultats/</t>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
         </is>
       </c>
       <c r="R261" s="10" t="n">
@@ -22941,7 +22941,7 @@
       </c>
       <c r="S261" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Chambéry (calendrier club) ; plage complète de la journée à confirmer sur lnh.fr</t>
+          <t>Plage de la journée selon le calendrier provisoire LNH</t>
         </is>
       </c>
       <c r="T261" s="9">
@@ -23018,7 +23018,7 @@
       </c>
       <c r="Q262" s="9" t="inlineStr">
         <is>
-          <t>https://www.psg.fr/content/le-calendrier-de-la-saison-2026-2027-de-la-daikin-starligue-devoile-psg-handball-saison-calendrier-2026-2027</t>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
         </is>
       </c>
       <c r="R262" s="10" t="n">
@@ -23026,7 +23026,7 @@
       </c>
       <c r="S262" s="9" t="inlineStr">
         <is>
-          <t>Plage 11-12-13 décembre (PSG/Montpellier)</t>
+          <t>Plage de la journée selon le calendrier provisoire LNH</t>
         </is>
       </c>
       <c r="T262" s="9">
@@ -23072,7 +23072,7 @@
         <v>46378</v>
       </c>
       <c r="I263" s="10" t="n">
-        <v>46378</v>
+        <v>46379</v>
       </c>
       <c r="J263" s="11" t="n"/>
       <c r="K263" s="9" t="inlineStr">
@@ -23103,7 +23103,7 @@
       </c>
       <c r="Q263" s="9" t="inlineStr">
         <is>
-          <t>https://www.teamchambe.com/equipe-premiere/calendrier-resultats/</t>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
         </is>
       </c>
       <c r="R263" s="10" t="n">
@@ -23111,7 +23111,7 @@
       </c>
       <c r="S263" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Chambéry (calendrier club) ; plage complète de la journée à confirmer sur lnh.fr</t>
+          <t>Journée en semaine (mar.–mer.) avant la trêve</t>
         </is>
       </c>
       <c r="T263" s="9">
@@ -23188,7 +23188,7 @@
       </c>
       <c r="Q264" s="9" t="inlineStr">
         <is>
-          <t>https://www.montpellierhandball.com/fr/actualites/2026-07-09/decouvrez-le-calendrier-26-27-de-la-daikin-starligue</t>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
         </is>
       </c>
       <c r="R264" s="10" t="n">
@@ -23196,7 +23196,7 @@
       </c>
       <c r="S264" s="9" t="inlineStr">
         <is>
-          <t>Reprise après la trêve internationale, plage 5-6-7 février</t>
+          <t>Plage de la journée selon le calendrier provisoire LNH</t>
         </is>
       </c>
       <c r="T264" s="9">
@@ -23242,7 +23242,7 @@
         <v>46430</v>
       </c>
       <c r="I265" s="10" t="n">
-        <v>46430</v>
+        <v>46432</v>
       </c>
       <c r="J265" s="11" t="n"/>
       <c r="K265" s="9" t="inlineStr">
@@ -23273,7 +23273,7 @@
       </c>
       <c r="Q265" s="9" t="inlineStr">
         <is>
-          <t>https://www.teamchambe.com/equipe-premiere/calendrier-resultats/</t>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
         </is>
       </c>
       <c r="R265" s="10" t="n">
@@ -23281,7 +23281,7 @@
       </c>
       <c r="S265" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Chambéry (calendrier club) ; plage complète de la journée à confirmer sur lnh.fr</t>
+          <t>Plage de la journée selon le calendrier provisoire LNH</t>
         </is>
       </c>
       <c r="T265" s="9">
@@ -23327,7 +23327,7 @@
         <v>46437</v>
       </c>
       <c r="I266" s="10" t="n">
-        <v>46437</v>
+        <v>46439</v>
       </c>
       <c r="J266" s="11" t="n"/>
       <c r="K266" s="9" t="inlineStr">
@@ -23358,7 +23358,7 @@
       </c>
       <c r="Q266" s="9" t="inlineStr">
         <is>
-          <t>https://www.teamchambe.com/equipe-premiere/calendrier-resultats/</t>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
         </is>
       </c>
       <c r="R266" s="10" t="n">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="S266" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Chambéry (calendrier club) ; plage complète de la journée à confirmer sur lnh.fr</t>
+          <t>Plage de la journée selon le calendrier provisoire LNH</t>
         </is>
       </c>
       <c r="T266" s="9">
@@ -23412,7 +23412,7 @@
         <v>46444</v>
       </c>
       <c r="I267" s="10" t="n">
-        <v>46444</v>
+        <v>46446</v>
       </c>
       <c r="J267" s="11" t="n"/>
       <c r="K267" s="9" t="inlineStr">
@@ -23443,7 +23443,7 @@
       </c>
       <c r="Q267" s="9" t="inlineStr">
         <is>
-          <t>https://www.teamchambe.com/equipe-premiere/calendrier-resultats/</t>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
         </is>
       </c>
       <c r="R267" s="10" t="n">
@@ -23451,7 +23451,7 @@
       </c>
       <c r="S267" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Chambéry (calendrier club) ; plage complète de la journée à confirmer sur lnh.fr</t>
+          <t>Plage de la journée selon le calendrier provisoire LNH</t>
         </is>
       </c>
       <c r="T267" s="9">
@@ -23497,7 +23497,7 @@
         <v>46451</v>
       </c>
       <c r="I268" s="10" t="n">
-        <v>46451</v>
+        <v>46453</v>
       </c>
       <c r="J268" s="11" t="n"/>
       <c r="K268" s="9" t="inlineStr">
@@ -23528,7 +23528,7 @@
       </c>
       <c r="Q268" s="9" t="inlineStr">
         <is>
-          <t>https://www.teamchambe.com/equipe-premiere/calendrier-resultats/</t>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
         </is>
       </c>
       <c r="R268" s="10" t="n">
@@ -23536,7 +23536,7 @@
       </c>
       <c r="S268" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Chambéry (calendrier club) ; plage complète de la journée à confirmer sur lnh.fr</t>
+          <t>Plage de la journée selon le calendrier provisoire LNH</t>
         </is>
       </c>
       <c r="T268" s="9">
@@ -23582,7 +23582,7 @@
         <v>46465</v>
       </c>
       <c r="I269" s="10" t="n">
-        <v>46465</v>
+        <v>46467</v>
       </c>
       <c r="J269" s="11" t="n"/>
       <c r="K269" s="9" t="inlineStr">
@@ -23613,7 +23613,7 @@
       </c>
       <c r="Q269" s="9" t="inlineStr">
         <is>
-          <t>https://www.teamchambe.com/equipe-premiere/calendrier-resultats/</t>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
         </is>
       </c>
       <c r="R269" s="10" t="n">
@@ -23621,7 +23621,7 @@
       </c>
       <c r="S269" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Chambéry (calendrier club) ; plage complète de la journée à confirmer sur lnh.fr</t>
+          <t>Plage de la journée selon le calendrier provisoire LNH</t>
         </is>
       </c>
       <c r="T269" s="9">
@@ -23667,7 +23667,7 @@
         <v>46472</v>
       </c>
       <c r="I270" s="10" t="n">
-        <v>46472</v>
+        <v>46474</v>
       </c>
       <c r="J270" s="11" t="n"/>
       <c r="K270" s="9" t="inlineStr">
@@ -23698,7 +23698,7 @@
       </c>
       <c r="Q270" s="9" t="inlineStr">
         <is>
-          <t>https://www.teamchambe.com/equipe-premiere/calendrier-resultats/</t>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
         </is>
       </c>
       <c r="R270" s="10" t="n">
@@ -23706,7 +23706,7 @@
       </c>
       <c r="S270" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Chambéry (calendrier club) ; plage complète de la journée à confirmer sur lnh.fr</t>
+          <t>Plage de la journée selon le calendrier provisoire LNH</t>
         </is>
       </c>
       <c r="T270" s="9">
@@ -23752,7 +23752,7 @@
         <v>46479</v>
       </c>
       <c r="I271" s="10" t="n">
-        <v>46479</v>
+        <v>46481</v>
       </c>
       <c r="J271" s="11" t="n"/>
       <c r="K271" s="9" t="inlineStr">
@@ -23783,7 +23783,7 @@
       </c>
       <c r="Q271" s="9" t="inlineStr">
         <is>
-          <t>https://www.teamchambe.com/equipe-premiere/calendrier-resultats/</t>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
         </is>
       </c>
       <c r="R271" s="10" t="n">
@@ -23791,7 +23791,7 @@
       </c>
       <c r="S271" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Chambéry (calendrier club) ; plage complète de la journée à confirmer sur lnh.fr</t>
+          <t>Plage de la journée selon le calendrier provisoire LNH</t>
         </is>
       </c>
       <c r="T271" s="9">
@@ -23837,7 +23837,7 @@
         <v>46486</v>
       </c>
       <c r="I272" s="10" t="n">
-        <v>46486</v>
+        <v>46488</v>
       </c>
       <c r="J272" s="11" t="n"/>
       <c r="K272" s="9" t="inlineStr">
@@ -23868,7 +23868,7 @@
       </c>
       <c r="Q272" s="9" t="inlineStr">
         <is>
-          <t>https://www.teamchambe.com/equipe-premiere/calendrier-resultats/</t>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
         </is>
       </c>
       <c r="R272" s="10" t="n">
@@ -23876,7 +23876,7 @@
       </c>
       <c r="S272" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Chambéry (calendrier club) ; plage complète de la journée à confirmer sur lnh.fr</t>
+          <t>Plage de la journée selon le calendrier provisoire LNH</t>
         </is>
       </c>
       <c r="T272" s="9">
@@ -23922,7 +23922,7 @@
         <v>46490</v>
       </c>
       <c r="I273" s="10" t="n">
-        <v>46490</v>
+        <v>46491</v>
       </c>
       <c r="J273" s="11" t="n"/>
       <c r="K273" s="9" t="inlineStr">
@@ -23953,7 +23953,7 @@
       </c>
       <c r="Q273" s="9" t="inlineStr">
         <is>
-          <t>https://www.teamchambe.com/equipe-premiere/calendrier-resultats/</t>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
         </is>
       </c>
       <c r="R273" s="10" t="n">
@@ -23961,7 +23961,7 @@
       </c>
       <c r="S273" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Chambéry (calendrier club) ; plage complète de la journée à confirmer sur lnh.fr</t>
+          <t>Journée en semaine (mar.–mer.)</t>
         </is>
       </c>
       <c r="T273" s="9">
@@ -24007,7 +24007,7 @@
         <v>46493</v>
       </c>
       <c r="I274" s="10" t="n">
-        <v>46493</v>
+        <v>46495</v>
       </c>
       <c r="J274" s="11" t="n"/>
       <c r="K274" s="9" t="inlineStr">
@@ -24038,7 +24038,7 @@
       </c>
       <c r="Q274" s="9" t="inlineStr">
         <is>
-          <t>https://www.teamchambe.com/equipe-premiere/calendrier-resultats/</t>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
         </is>
       </c>
       <c r="R274" s="10" t="n">
@@ -24046,7 +24046,7 @@
       </c>
       <c r="S274" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Chambéry (calendrier club) ; plage complète de la journée à confirmer sur lnh.fr</t>
+          <t>Plage de la journée selon le calendrier provisoire LNH</t>
         </is>
       </c>
       <c r="T274" s="9">
@@ -24092,7 +24092,7 @@
         <v>46500</v>
       </c>
       <c r="I275" s="10" t="n">
-        <v>46500</v>
+        <v>46502</v>
       </c>
       <c r="J275" s="11" t="n"/>
       <c r="K275" s="9" t="inlineStr">
@@ -24123,7 +24123,7 @@
       </c>
       <c r="Q275" s="9" t="inlineStr">
         <is>
-          <t>https://www.teamchambe.com/equipe-premiere/calendrier-resultats/</t>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
         </is>
       </c>
       <c r="R275" s="10" t="n">
@@ -24131,7 +24131,7 @@
       </c>
       <c r="S275" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Chambéry (calendrier club) ; plage complète de la journée à confirmer sur lnh.fr</t>
+          <t>Plage de la journée selon le calendrier provisoire LNH</t>
         </is>
       </c>
       <c r="T275" s="9">
@@ -24177,7 +24177,7 @@
         <v>46507</v>
       </c>
       <c r="I276" s="10" t="n">
-        <v>46507</v>
+        <v>46509</v>
       </c>
       <c r="J276" s="11" t="n"/>
       <c r="K276" s="9" t="inlineStr">
@@ -24208,7 +24208,7 @@
       </c>
       <c r="Q276" s="9" t="inlineStr">
         <is>
-          <t>https://www.teamchambe.com/equipe-premiere/calendrier-resultats/</t>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
         </is>
       </c>
       <c r="R276" s="10" t="n">
@@ -24216,7 +24216,7 @@
       </c>
       <c r="S276" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Chambéry (calendrier club) ; plage complète de la journée à confirmer sur lnh.fr</t>
+          <t>Plage de la journée selon le calendrier provisoire LNH</t>
         </is>
       </c>
       <c r="T276" s="9">
@@ -24259,10 +24259,10 @@
         </is>
       </c>
       <c r="H277" s="10" t="n">
-        <v>46521</v>
+        <v>46519</v>
       </c>
       <c r="I277" s="10" t="n">
-        <v>46521</v>
+        <v>46522</v>
       </c>
       <c r="J277" s="11" t="n"/>
       <c r="K277" s="9" t="inlineStr">
@@ -24293,7 +24293,7 @@
       </c>
       <c r="Q277" s="9" t="inlineStr">
         <is>
-          <t>https://www.teamchambe.com/equipe-premiere/calendrier-resultats/</t>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
         </is>
       </c>
       <c r="R277" s="10" t="n">
@@ -24301,7 +24301,7 @@
       </c>
       <c r="S277" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Chambéry (calendrier club) ; plage complète de la journée à confirmer sur lnh.fr</t>
+          <t>Plage de la journée selon le calendrier provisoire LNH</t>
         </is>
       </c>
       <c r="T277" s="9">
@@ -24378,7 +24378,7 @@
       </c>
       <c r="Q278" s="9" t="inlineStr">
         <is>
-          <t>https://docs.lnh.fr/dp/</t>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
         </is>
       </c>
       <c r="R278" s="10" t="n">
@@ -24386,7 +24386,7 @@
       </c>
       <c r="S278" s="9" t="inlineStr">
         <is>
-          <t>Dernière journée (mercredi 19 mai selon calendrier ; le médiaguide écrit « samedi »)</t>
+          <t>Dernière journée (mercredi)</t>
         </is>
       </c>
       <c r="T278" s="9">
@@ -24552,7 +24552,7 @@
       </c>
       <c r="S280" s="9" t="inlineStr">
         <is>
-          <t>Match unique en lieu neutre, lieu à définir</t>
+          <t>Match unique en lieu neutre, lieu à définir ; le calendrier provisoire LNH de février 2026 indiquait le vendredi 04/06</t>
         </is>
       </c>
       <c r="T280" s="9">
@@ -28471,7 +28471,7 @@
       </c>
       <c r="C329" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D329" s="9" t="inlineStr">
@@ -28489,7 +28489,7 @@
       </c>
       <c r="G329" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Journée 1</t>
+          <t>Alterna Volstar – Journée 1</t>
         </is>
       </c>
       <c r="H329" s="10" t="n">
@@ -28535,7 +28535,7 @@
       </c>
       <c r="S329" s="9" t="inlineStr">
         <is>
-          <t>Reprise D1M le 17 octobre 2026 (LNV) ; 14 clubs. Compétition renommée D1M / Alterna Volstar</t>
+          <t>Reprise D1M le 17 octobre 2026 (LNV) ; 14 clubs</t>
         </is>
       </c>
       <c r="T329" s="9">
@@ -28556,7 +28556,7 @@
       </c>
       <c r="C330" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D330" s="9" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="G330" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Journée 2</t>
+          <t>Alterna Volstar – Journée 2</t>
         </is>
       </c>
       <c r="H330" s="10" t="n">
@@ -28620,7 +28620,7 @@
       </c>
       <c r="S330" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr. Compétition renommée D1M / Alterna Volstar par la LNV</t>
+          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr</t>
         </is>
       </c>
       <c r="T330" s="9">
@@ -28641,7 +28641,7 @@
       </c>
       <c r="C331" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D331" s="9" t="inlineStr">
@@ -28659,7 +28659,7 @@
       </c>
       <c r="G331" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Journée 3</t>
+          <t>Alterna Volstar – Journée 3</t>
         </is>
       </c>
       <c r="H331" s="10" t="n">
@@ -28705,7 +28705,7 @@
       </c>
       <c r="S331" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr. Compétition renommée D1M / Alterna Volstar par la LNV</t>
+          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr</t>
         </is>
       </c>
       <c r="T331" s="9">
@@ -28726,7 +28726,7 @@
       </c>
       <c r="C332" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D332" s="9" t="inlineStr">
@@ -28744,7 +28744,7 @@
       </c>
       <c r="G332" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Journée 4</t>
+          <t>Alterna Volstar – Journée 4</t>
         </is>
       </c>
       <c r="H332" s="10" t="n">
@@ -28790,7 +28790,7 @@
       </c>
       <c r="S332" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr. Compétition renommée D1M / Alterna Volstar par la LNV</t>
+          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr</t>
         </is>
       </c>
       <c r="T332" s="9">
@@ -28811,7 +28811,7 @@
       </c>
       <c r="C333" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D333" s="9" t="inlineStr">
@@ -28829,7 +28829,7 @@
       </c>
       <c r="G333" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Journée 5</t>
+          <t>Alterna Volstar – Journée 5</t>
         </is>
       </c>
       <c r="H333" s="10" t="n">
@@ -28875,7 +28875,7 @@
       </c>
       <c r="S333" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr. Compétition renommée D1M / Alterna Volstar par la LNV</t>
+          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr</t>
         </is>
       </c>
       <c r="T333" s="9">
@@ -28896,7 +28896,7 @@
       </c>
       <c r="C334" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D334" s="9" t="inlineStr">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="G334" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Journée 6</t>
+          <t>Alterna Volstar – Journée 6</t>
         </is>
       </c>
       <c r="H334" s="10" t="n">
@@ -28960,7 +28960,7 @@
       </c>
       <c r="S334" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr. Compétition renommée D1M / Alterna Volstar par la LNV</t>
+          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr</t>
         </is>
       </c>
       <c r="T334" s="9">
@@ -28981,7 +28981,7 @@
       </c>
       <c r="C335" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D335" s="9" t="inlineStr">
@@ -28999,7 +28999,7 @@
       </c>
       <c r="G335" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Journée 8</t>
+          <t>Alterna Volstar – Journée 8</t>
         </is>
       </c>
       <c r="H335" s="10" t="n">
@@ -29045,7 +29045,7 @@
       </c>
       <c r="S335" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr. Compétition renommée D1M / Alterna Volstar par la LNV</t>
+          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr</t>
         </is>
       </c>
       <c r="T335" s="9">
@@ -29066,7 +29066,7 @@
       </c>
       <c r="C336" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D336" s="9" t="inlineStr">
@@ -29084,7 +29084,7 @@
       </c>
       <c r="G336" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Journée 9</t>
+          <t>Alterna Volstar – Journée 9</t>
         </is>
       </c>
       <c r="H336" s="10" t="n">
@@ -29130,7 +29130,7 @@
       </c>
       <c r="S336" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr. Compétition renommée D1M / Alterna Volstar par la LNV</t>
+          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr</t>
         </is>
       </c>
       <c r="T336" s="9">
@@ -29151,7 +29151,7 @@
       </c>
       <c r="C337" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D337" s="9" t="inlineStr">
@@ -29169,7 +29169,7 @@
       </c>
       <c r="G337" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Journée 10</t>
+          <t>Alterna Volstar – Journée 10</t>
         </is>
       </c>
       <c r="H337" s="10" t="n">
@@ -29215,7 +29215,7 @@
       </c>
       <c r="S337" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr. Compétition renommée D1M / Alterna Volstar par la LNV</t>
+          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr</t>
         </is>
       </c>
       <c r="T337" s="9">
@@ -29236,7 +29236,7 @@
       </c>
       <c r="C338" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D338" s="9" t="inlineStr">
@@ -29254,7 +29254,7 @@
       </c>
       <c r="G338" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Journée 11</t>
+          <t>Alterna Volstar – Journée 11</t>
         </is>
       </c>
       <c r="H338" s="10" t="n">
@@ -29300,7 +29300,7 @@
       </c>
       <c r="S338" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr. Compétition renommée D1M / Alterna Volstar par la LNV</t>
+          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr</t>
         </is>
       </c>
       <c r="T338" s="9">
@@ -29321,7 +29321,7 @@
       </c>
       <c r="C339" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D339" s="9" t="inlineStr">
@@ -29339,7 +29339,7 @@
       </c>
       <c r="G339" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Journée 12</t>
+          <t>Alterna Volstar – Journée 12</t>
         </is>
       </c>
       <c r="H339" s="10" t="n">
@@ -29385,7 +29385,7 @@
       </c>
       <c r="S339" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr. Compétition renommée D1M / Alterna Volstar par la LNV</t>
+          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr</t>
         </is>
       </c>
       <c r="T339" s="9">
@@ -29406,7 +29406,7 @@
       </c>
       <c r="C340" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D340" s="9" t="inlineStr">
@@ -29424,7 +29424,7 @@
       </c>
       <c r="G340" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Journée 13</t>
+          <t>Alterna Volstar – Journée 13</t>
         </is>
       </c>
       <c r="H340" s="10" t="n">
@@ -29470,7 +29470,7 @@
       </c>
       <c r="S340" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr. Compétition renommée D1M / Alterna Volstar par la LNV</t>
+          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr</t>
         </is>
       </c>
       <c r="T340" s="9">
@@ -29491,7 +29491,7 @@
       </c>
       <c r="C341" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D341" s="9" t="inlineStr">
@@ -29509,7 +29509,7 @@
       </c>
       <c r="G341" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Journée 14</t>
+          <t>Alterna Volstar – Journée 14</t>
         </is>
       </c>
       <c r="H341" s="10" t="n">
@@ -29555,7 +29555,7 @@
       </c>
       <c r="S341" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr. Compétition renommée D1M / Alterna Volstar par la LNV</t>
+          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr</t>
         </is>
       </c>
       <c r="T341" s="9">
@@ -29576,7 +29576,7 @@
       </c>
       <c r="C342" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D342" s="9" t="inlineStr">
@@ -29594,7 +29594,7 @@
       </c>
       <c r="G342" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Journée 15</t>
+          <t>Alterna Volstar – Journée 15</t>
         </is>
       </c>
       <c r="H342" s="10" t="n">
@@ -29640,7 +29640,7 @@
       </c>
       <c r="S342" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr. Compétition renommée D1M / Alterna Volstar par la LNV</t>
+          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr</t>
         </is>
       </c>
       <c r="T342" s="9">
@@ -29661,7 +29661,7 @@
       </c>
       <c r="C343" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D343" s="9" t="inlineStr">
@@ -29679,7 +29679,7 @@
       </c>
       <c r="G343" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Journée 16</t>
+          <t>Alterna Volstar – Journée 16</t>
         </is>
       </c>
       <c r="H343" s="10" t="n">
@@ -29725,7 +29725,7 @@
       </c>
       <c r="S343" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr. Compétition renommée D1M / Alterna Volstar par la LNV</t>
+          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr</t>
         </is>
       </c>
       <c r="T343" s="9">
@@ -29746,7 +29746,7 @@
       </c>
       <c r="C344" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D344" s="9" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="G344" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Journée 17</t>
+          <t>Alterna Volstar – Journée 17</t>
         </is>
       </c>
       <c r="H344" s="10" t="n">
@@ -29810,7 +29810,7 @@
       </c>
       <c r="S344" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr. Compétition renommée D1M / Alterna Volstar par la LNV</t>
+          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr</t>
         </is>
       </c>
       <c r="T344" s="9">
@@ -29831,7 +29831,7 @@
       </c>
       <c r="C345" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D345" s="9" t="inlineStr">
@@ -29849,7 +29849,7 @@
       </c>
       <c r="G345" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Journée 18</t>
+          <t>Alterna Volstar – Journée 18</t>
         </is>
       </c>
       <c r="H345" s="10" t="n">
@@ -29895,7 +29895,7 @@
       </c>
       <c r="S345" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr. Compétition renommée D1M / Alterna Volstar par la LNV</t>
+          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr</t>
         </is>
       </c>
       <c r="T345" s="9">
@@ -29916,7 +29916,7 @@
       </c>
       <c r="C346" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D346" s="9" t="inlineStr">
@@ -29934,7 +29934,7 @@
       </c>
       <c r="G346" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Journée 19</t>
+          <t>Alterna Volstar – Journée 19</t>
         </is>
       </c>
       <c r="H346" s="10" t="n">
@@ -29980,7 +29980,7 @@
       </c>
       <c r="S346" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr. Compétition renommée D1M / Alterna Volstar par la LNV</t>
+          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr</t>
         </is>
       </c>
       <c r="T346" s="9">
@@ -30001,7 +30001,7 @@
       </c>
       <c r="C347" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D347" s="9" t="inlineStr">
@@ -30019,7 +30019,7 @@
       </c>
       <c r="G347" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Journée 20</t>
+          <t>Alterna Volstar – Journée 20</t>
         </is>
       </c>
       <c r="H347" s="10" t="n">
@@ -30065,7 +30065,7 @@
       </c>
       <c r="S347" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr. Compétition renommée D1M / Alterna Volstar par la LNV</t>
+          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr</t>
         </is>
       </c>
       <c r="T347" s="9">
@@ -30086,7 +30086,7 @@
       </c>
       <c r="C348" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D348" s="9" t="inlineStr">
@@ -30104,7 +30104,7 @@
       </c>
       <c r="G348" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Journée 21</t>
+          <t>Alterna Volstar – Journée 21</t>
         </is>
       </c>
       <c r="H348" s="10" t="n">
@@ -30150,7 +30150,7 @@
       </c>
       <c r="S348" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr. Compétition renommée D1M / Alterna Volstar par la LNV</t>
+          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr</t>
         </is>
       </c>
       <c r="T348" s="9">
@@ -30171,7 +30171,7 @@
       </c>
       <c r="C349" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D349" s="9" t="inlineStr">
@@ -30189,7 +30189,7 @@
       </c>
       <c r="G349" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Journée 22</t>
+          <t>Alterna Volstar – Journée 22</t>
         </is>
       </c>
       <c r="H349" s="10" t="n">
@@ -30235,7 +30235,7 @@
       </c>
       <c r="S349" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr. Compétition renommée D1M / Alterna Volstar par la LNV</t>
+          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr</t>
         </is>
       </c>
       <c r="T349" s="9">
@@ -30256,7 +30256,7 @@
       </c>
       <c r="C350" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D350" s="9" t="inlineStr">
@@ -30274,7 +30274,7 @@
       </c>
       <c r="G350" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Journée 23</t>
+          <t>Alterna Volstar – Journée 23</t>
         </is>
       </c>
       <c r="H350" s="10" t="n">
@@ -30320,7 +30320,7 @@
       </c>
       <c r="S350" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr. Compétition renommée D1M / Alterna Volstar par la LNV</t>
+          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr</t>
         </is>
       </c>
       <c r="T350" s="9">
@@ -30341,7 +30341,7 @@
       </c>
       <c r="C351" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D351" s="9" t="inlineStr">
@@ -30359,7 +30359,7 @@
       </c>
       <c r="G351" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Journée 24</t>
+          <t>Alterna Volstar – Journée 24</t>
         </is>
       </c>
       <c r="H351" s="10" t="n">
@@ -30405,7 +30405,7 @@
       </c>
       <c r="S351" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr. Compétition renommée D1M / Alterna Volstar par la LNV</t>
+          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr</t>
         </is>
       </c>
       <c r="T351" s="9">
@@ -30426,7 +30426,7 @@
       </c>
       <c r="C352" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D352" s="9" t="inlineStr">
@@ -30444,7 +30444,7 @@
       </c>
       <c r="G352" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Journée 25</t>
+          <t>Alterna Volstar – Journée 25</t>
         </is>
       </c>
       <c r="H352" s="10" t="n">
@@ -30490,7 +30490,7 @@
       </c>
       <c r="S352" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr. Compétition renommée D1M / Alterna Volstar par la LNV</t>
+          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr</t>
         </is>
       </c>
       <c r="T352" s="9">
@@ -30511,7 +30511,7 @@
       </c>
       <c r="C353" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D353" s="9" t="inlineStr">
@@ -30529,7 +30529,7 @@
       </c>
       <c r="G353" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Journée 26</t>
+          <t>Alterna Volstar – Journée 26</t>
         </is>
       </c>
       <c r="H353" s="10" t="n">
@@ -30575,7 +30575,7 @@
       </c>
       <c r="S353" s="9" t="inlineStr">
         <is>
-          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr. Compétition renommée D1M / Alterna Volstar par la LNV</t>
+          <t>Date du match de Royan (calendrier club) ; plage complète de la journée à confirmer sur lnv.fr</t>
         </is>
       </c>
       <c r="T353" s="9">
@@ -30596,7 +30596,7 @@
       </c>
       <c r="C354" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D354" s="9" t="inlineStr">
@@ -30612,7 +30612,7 @@
       <c r="F354" s="9" t="n"/>
       <c r="G354" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Demi-finales</t>
+          <t>Alterna Volstar – Demi-finales</t>
         </is>
       </c>
       <c r="H354" s="10" t="n"/>
@@ -30675,7 +30675,7 @@
       </c>
       <c r="C355" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D355" s="9" t="inlineStr">
@@ -30691,7 +30691,7 @@
       <c r="F355" s="9" t="n"/>
       <c r="G355" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Finale</t>
+          <t>Alterna Volstar – Finale</t>
         </is>
       </c>
       <c r="H355" s="10" t="n"/>
@@ -30754,7 +30754,7 @@
       </c>
       <c r="C356" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D356" s="9" t="inlineStr">
@@ -30772,7 +30772,7 @@
       </c>
       <c r="G356" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Journée 7</t>
+          <t>Alterna Volstar – Journée 7</t>
         </is>
       </c>
       <c r="H356" s="10" t="n"/>
@@ -30835,7 +30835,7 @@
       </c>
       <c r="C357" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D357" s="9" t="inlineStr">
@@ -30851,7 +30851,7 @@
       <c r="F357" s="9" t="n"/>
       <c r="G357" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Play-in</t>
+          <t>Alterna Volstar – Play-in</t>
         </is>
       </c>
       <c r="H357" s="10" t="n"/>
@@ -30914,7 +30914,7 @@
       </c>
       <c r="C358" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D358" s="9" t="inlineStr">
@@ -30930,7 +30930,7 @@
       <c r="F358" s="9" t="n"/>
       <c r="G358" s="9" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue – Quarts de finale</t>
+          <t>Alterna Volstar – Quarts de finale</t>
         </is>
       </c>
       <c r="H358" s="10" t="n"/>
@@ -65212,14 +65212,3931 @@
         <v/>
       </c>
     </row>
+    <row r="753">
+      <c r="A753" s="9" t="inlineStr">
+        <is>
+          <t>SL-2627-033</t>
+        </is>
+      </c>
+      <c r="B753" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C753" s="9" t="inlineStr">
+        <is>
+          <t>StarLigue</t>
+        </is>
+      </c>
+      <c r="D753" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E753" s="9" t="inlineStr">
+        <is>
+          <t>Finale places 5 à 8</t>
+        </is>
+      </c>
+      <c r="F753" s="9" t="inlineStr">
+        <is>
+          <t>Aller</t>
+        </is>
+      </c>
+      <c r="G753" s="9" t="inlineStr">
+        <is>
+          <t>StarLigue – Finale des play-offs 5 à 8 (aller)</t>
+        </is>
+      </c>
+      <c r="H753" s="10" t="n">
+        <v>46539</v>
+      </c>
+      <c r="I753" s="10" t="n">
+        <v>46539</v>
+      </c>
+      <c r="J753" s="11" t="n"/>
+      <c r="K753" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L753" s="9" t="n"/>
+      <c r="M753" s="9" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="N753" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O753" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P753" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q753" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R753" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S753" s="9" t="n"/>
+      <c r="T753" s="9">
+        <f>IF(H753="","",IF(MAX(H753,I753)&lt;TODAY(),"Terminé",IF(H753&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="9" t="inlineStr">
+        <is>
+          <t>SL-2627-034</t>
+        </is>
+      </c>
+      <c r="B754" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C754" s="9" t="inlineStr">
+        <is>
+          <t>StarLigue</t>
+        </is>
+      </c>
+      <c r="D754" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E754" s="9" t="inlineStr">
+        <is>
+          <t>Finale places 5 à 8</t>
+        </is>
+      </c>
+      <c r="F754" s="9" t="inlineStr">
+        <is>
+          <t>Retour</t>
+        </is>
+      </c>
+      <c r="G754" s="9" t="inlineStr">
+        <is>
+          <t>StarLigue – Finale des play-offs 5 à 8 (retour)</t>
+        </is>
+      </c>
+      <c r="H754" s="10" t="n">
+        <v>46543</v>
+      </c>
+      <c r="I754" s="10" t="n">
+        <v>46543</v>
+      </c>
+      <c r="J754" s="11" t="n"/>
+      <c r="K754" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L754" s="9" t="n"/>
+      <c r="M754" s="9" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="N754" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O754" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P754" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q754" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R754" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S754" s="9" t="n"/>
+      <c r="T754" s="9">
+        <f>IF(H754="","",IF(MAX(H754,I754)&lt;TODAY(),"Terminé",IF(H754&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="9" t="inlineStr">
+        <is>
+          <t>TDCH-2627-001</t>
+        </is>
+      </c>
+      <c r="B755" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C755" s="9" t="inlineStr">
+        <is>
+          <t>Trophée des Champions de handball</t>
+        </is>
+      </c>
+      <c r="D755" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E755" s="9" t="inlineStr">
+        <is>
+          <t>Finale</t>
+        </is>
+      </c>
+      <c r="F755" s="9" t="n"/>
+      <c r="G755" s="9" t="inlineStr">
+        <is>
+          <t>Trophée des Champions 2026</t>
+        </is>
+      </c>
+      <c r="H755" s="10" t="n">
+        <v>46263</v>
+      </c>
+      <c r="I755" s="10" t="n">
+        <v>46263</v>
+      </c>
+      <c r="J755" s="11" t="n"/>
+      <c r="K755" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L755" s="9" t="n"/>
+      <c r="M755" s="9" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="N755" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O755" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P755" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q755" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R755" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S755" s="9" t="inlineStr">
+        <is>
+          <t>Événement LNH ; déjà disputé</t>
+        </is>
+      </c>
+      <c r="T755" s="9">
+        <f>IF(H755="","",IF(MAX(H755,I755)&lt;TODAY(),"Terminé",IF(H755&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="9" t="inlineStr">
+        <is>
+          <t>CDFH-2627-001</t>
+        </is>
+      </c>
+      <c r="B756" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C756" s="9" t="inlineStr">
+        <is>
+          <t>Coupe de France de handball</t>
+        </is>
+      </c>
+      <c r="D756" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E756" s="9" t="inlineStr">
+        <is>
+          <t>1er tour</t>
+        </is>
+      </c>
+      <c r="F756" s="9" t="n"/>
+      <c r="G756" s="9" t="inlineStr">
+        <is>
+          <t>Coupe de France – 1er tour</t>
+        </is>
+      </c>
+      <c r="H756" s="10" t="n">
+        <v>46264</v>
+      </c>
+      <c r="I756" s="10" t="n">
+        <v>46264</v>
+      </c>
+      <c r="J756" s="11" t="n"/>
+      <c r="K756" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L756" s="9" t="n"/>
+      <c r="M756" s="9" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="N756" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O756" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P756" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q756" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R756" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S756" s="9" t="inlineStr">
+        <is>
+          <t>Déjà disputé</t>
+        </is>
+      </c>
+      <c r="T756" s="9">
+        <f>IF(H756="","",IF(MAX(H756,I756)&lt;TODAY(),"Terminé",IF(H756&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="9" t="inlineStr">
+        <is>
+          <t>CDFH-2627-002</t>
+        </is>
+      </c>
+      <c r="B757" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C757" s="9" t="inlineStr">
+        <is>
+          <t>Coupe de France de handball</t>
+        </is>
+      </c>
+      <c r="D757" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E757" s="9" t="inlineStr">
+        <is>
+          <t>2e tour</t>
+        </is>
+      </c>
+      <c r="F757" s="9" t="n"/>
+      <c r="G757" s="9" t="inlineStr">
+        <is>
+          <t>Coupe de France – 2e tour</t>
+        </is>
+      </c>
+      <c r="H757" s="10" t="n">
+        <v>46294</v>
+      </c>
+      <c r="I757" s="10" t="n">
+        <v>46295</v>
+      </c>
+      <c r="J757" s="11" t="n"/>
+      <c r="K757" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L757" s="9" t="n"/>
+      <c r="M757" s="9" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="N757" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O757" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P757" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q757" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R757" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S757" s="9" t="inlineStr">
+        <is>
+          <t>Déjà disputé</t>
+        </is>
+      </c>
+      <c r="T757" s="9">
+        <f>IF(H757="","",IF(MAX(H757,I757)&lt;TODAY(),"Terminé",IF(H757&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="9" t="inlineStr">
+        <is>
+          <t>CDFH-2627-003</t>
+        </is>
+      </c>
+      <c r="B758" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C758" s="9" t="inlineStr">
+        <is>
+          <t>Coupe de France de handball</t>
+        </is>
+      </c>
+      <c r="D758" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E758" s="9" t="inlineStr">
+        <is>
+          <t>3e tour</t>
+        </is>
+      </c>
+      <c r="F758" s="9" t="n"/>
+      <c r="G758" s="9" t="inlineStr">
+        <is>
+          <t>Coupe de France – 3e tour</t>
+        </is>
+      </c>
+      <c r="H758" s="10" t="n">
+        <v>46322</v>
+      </c>
+      <c r="I758" s="10" t="n">
+        <v>46323</v>
+      </c>
+      <c r="J758" s="11" t="n"/>
+      <c r="K758" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L758" s="9" t="n"/>
+      <c r="M758" s="9" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="N758" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O758" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P758" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q758" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R758" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S758" s="9" t="n"/>
+      <c r="T758" s="9">
+        <f>IF(H758="","",IF(MAX(H758,I758)&lt;TODAY(),"Terminé",IF(H758&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="9" t="inlineStr">
+        <is>
+          <t>CDFH-2627-004</t>
+        </is>
+      </c>
+      <c r="B759" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C759" s="9" t="inlineStr">
+        <is>
+          <t>Coupe de France de handball</t>
+        </is>
+      </c>
+      <c r="D759" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E759" s="9" t="inlineStr">
+        <is>
+          <t>Quarts de finale</t>
+        </is>
+      </c>
+      <c r="F759" s="9" t="n"/>
+      <c r="G759" s="9" t="inlineStr">
+        <is>
+          <t>Coupe de France – Quarts de finale</t>
+        </is>
+      </c>
+      <c r="H759" s="10" t="n">
+        <v>46374</v>
+      </c>
+      <c r="I759" s="10" t="n">
+        <v>46375</v>
+      </c>
+      <c r="J759" s="11" t="n"/>
+      <c r="K759" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L759" s="9" t="n"/>
+      <c r="M759" s="9" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="N759" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O759" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P759" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q759" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R759" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S759" s="9" t="n"/>
+      <c r="T759" s="9">
+        <f>IF(H759="","",IF(MAX(H759,I759)&lt;TODAY(),"Terminé",IF(H759&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="9" t="inlineStr">
+        <is>
+          <t>CDFH-2627-005</t>
+        </is>
+      </c>
+      <c r="B760" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C760" s="9" t="inlineStr">
+        <is>
+          <t>Coupe de France de handball</t>
+        </is>
+      </c>
+      <c r="D760" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E760" s="9" t="inlineStr">
+        <is>
+          <t>Demi-finales</t>
+        </is>
+      </c>
+      <c r="F760" s="9" t="n"/>
+      <c r="G760" s="9" t="inlineStr">
+        <is>
+          <t>Coupe de France – Demi-finales</t>
+        </is>
+      </c>
+      <c r="H760" s="10" t="n">
+        <v>46483</v>
+      </c>
+      <c r="I760" s="10" t="n">
+        <v>46484</v>
+      </c>
+      <c r="J760" s="11" t="n"/>
+      <c r="K760" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L760" s="9" t="n"/>
+      <c r="M760" s="9" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="N760" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O760" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P760" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q760" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R760" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S760" s="9" t="n"/>
+      <c r="T760" s="9">
+        <f>IF(H760="","",IF(MAX(H760,I760)&lt;TODAY(),"Terminé",IF(H760&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="9" t="inlineStr">
+        <is>
+          <t>CDFH-2627-006</t>
+        </is>
+      </c>
+      <c r="B761" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C761" s="9" t="inlineStr">
+        <is>
+          <t>Coupe de France de handball</t>
+        </is>
+      </c>
+      <c r="D761" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E761" s="9" t="inlineStr">
+        <is>
+          <t>Finale</t>
+        </is>
+      </c>
+      <c r="F761" s="9" t="n"/>
+      <c r="G761" s="9" t="inlineStr">
+        <is>
+          <t>Coupe de France – Finale</t>
+        </is>
+      </c>
+      <c r="H761" s="10" t="n">
+        <v>46523</v>
+      </c>
+      <c r="I761" s="10" t="n">
+        <v>46523</v>
+      </c>
+      <c r="J761" s="11" t="n"/>
+      <c r="K761" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L761" s="9" t="n"/>
+      <c r="M761" s="9" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="N761" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O761" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P761" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q761" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R761" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S761" s="9" t="n"/>
+      <c r="T761" s="9">
+        <f>IF(H761="","",IF(MAX(H761,I761)&lt;TODAY(),"Terminé",IF(H761&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="9" t="inlineStr">
+        <is>
+          <t>IHFSG-2627-001</t>
+        </is>
+      </c>
+      <c r="B762" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C762" s="9" t="inlineStr">
+        <is>
+          <t>IHF Super Globe</t>
+        </is>
+      </c>
+      <c r="D762" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E762" s="9" t="inlineStr">
+        <is>
+          <t>Compétition</t>
+        </is>
+      </c>
+      <c r="F762" s="9" t="n"/>
+      <c r="G762" s="9" t="inlineStr">
+        <is>
+          <t>IHF Super Globe 2026 (Mondial des clubs)</t>
+        </is>
+      </c>
+      <c r="H762" s="10" t="n">
+        <v>46290</v>
+      </c>
+      <c r="I762" s="10" t="n">
+        <v>46296</v>
+      </c>
+      <c r="J762" s="11" t="n"/>
+      <c r="K762" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L762" s="9" t="n"/>
+      <c r="M762" s="9" t="n"/>
+      <c r="N762" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O762" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P762" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q762" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R762" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S762" s="9" t="inlineStr">
+        <is>
+          <t>Déjà disputé ; lieu non précisé dans le calendrier LNH</t>
+        </is>
+      </c>
+      <c r="T762" s="9">
+        <f>IF(H762="","",IF(MAX(H762,I762)&lt;TODAY(),"Terminé",IF(H762&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="9" t="inlineStr">
+        <is>
+          <t>EHFCL-2627-001</t>
+        </is>
+      </c>
+      <c r="B763" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C763" s="9" t="inlineStr">
+        <is>
+          <t>EHF Champions League</t>
+        </is>
+      </c>
+      <c r="D763" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E763" s="9" t="inlineStr">
+        <is>
+          <t>Phase de groupes</t>
+        </is>
+      </c>
+      <c r="F763" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G763" s="9" t="inlineStr">
+        <is>
+          <t>Ligue des champions EHF – Journée 1</t>
+        </is>
+      </c>
+      <c r="H763" s="10" t="n">
+        <v>46274</v>
+      </c>
+      <c r="I763" s="10" t="n">
+        <v>46275</v>
+      </c>
+      <c r="J763" s="11" t="n"/>
+      <c r="K763" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L763" s="9" t="n"/>
+      <c r="M763" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N763" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O763" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P763" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q763" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R763" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S763" s="9" t="inlineStr">
+        <is>
+          <t>Repère GP1 du calendrier LNH</t>
+        </is>
+      </c>
+      <c r="T763" s="9">
+        <f>IF(H763="","",IF(MAX(H763,I763)&lt;TODAY(),"Terminé",IF(H763&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="9" t="inlineStr">
+        <is>
+          <t>EHFCL-2627-002</t>
+        </is>
+      </c>
+      <c r="B764" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C764" s="9" t="inlineStr">
+        <is>
+          <t>EHF Champions League</t>
+        </is>
+      </c>
+      <c r="D764" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E764" s="9" t="inlineStr">
+        <is>
+          <t>Phase de groupes</t>
+        </is>
+      </c>
+      <c r="F764" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G764" s="9" t="inlineStr">
+        <is>
+          <t>Ligue des champions EHF – Journée 2</t>
+        </is>
+      </c>
+      <c r="H764" s="10" t="n">
+        <v>46281</v>
+      </c>
+      <c r="I764" s="10" t="n">
+        <v>46282</v>
+      </c>
+      <c r="J764" s="11" t="n"/>
+      <c r="K764" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L764" s="9" t="n"/>
+      <c r="M764" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N764" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O764" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P764" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q764" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R764" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S764" s="9" t="inlineStr">
+        <is>
+          <t>Repère GP2 du calendrier LNH</t>
+        </is>
+      </c>
+      <c r="T764" s="9">
+        <f>IF(H764="","",IF(MAX(H764,I764)&lt;TODAY(),"Terminé",IF(H764&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="9" t="inlineStr">
+        <is>
+          <t>EHFCL-2627-003</t>
+        </is>
+      </c>
+      <c r="B765" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C765" s="9" t="inlineStr">
+        <is>
+          <t>EHF Champions League</t>
+        </is>
+      </c>
+      <c r="D765" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E765" s="9" t="inlineStr">
+        <is>
+          <t>Phase de groupes</t>
+        </is>
+      </c>
+      <c r="F765" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G765" s="9" t="inlineStr">
+        <is>
+          <t>Ligue des champions EHF – Journée 3</t>
+        </is>
+      </c>
+      <c r="H765" s="10" t="n">
+        <v>46302</v>
+      </c>
+      <c r="I765" s="10" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J765" s="11" t="n"/>
+      <c r="K765" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L765" s="9" t="n"/>
+      <c r="M765" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N765" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O765" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P765" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q765" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R765" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S765" s="9" t="inlineStr">
+        <is>
+          <t>Repère GP3 du calendrier LNH</t>
+        </is>
+      </c>
+      <c r="T765" s="9">
+        <f>IF(H765="","",IF(MAX(H765,I765)&lt;TODAY(),"Terminé",IF(H765&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="9" t="inlineStr">
+        <is>
+          <t>EHFCL-2627-004</t>
+        </is>
+      </c>
+      <c r="B766" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C766" s="9" t="inlineStr">
+        <is>
+          <t>EHF Champions League</t>
+        </is>
+      </c>
+      <c r="D766" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E766" s="9" t="inlineStr">
+        <is>
+          <t>Phase de groupes</t>
+        </is>
+      </c>
+      <c r="F766" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G766" s="9" t="inlineStr">
+        <is>
+          <t>Ligue des champions EHF – Journée 4</t>
+        </is>
+      </c>
+      <c r="H766" s="10" t="n">
+        <v>46309</v>
+      </c>
+      <c r="I766" s="10" t="n">
+        <v>46310</v>
+      </c>
+      <c r="J766" s="11" t="n"/>
+      <c r="K766" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L766" s="9" t="n"/>
+      <c r="M766" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N766" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O766" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P766" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q766" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R766" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S766" s="9" t="inlineStr">
+        <is>
+          <t>Repère GP4 du calendrier LNH</t>
+        </is>
+      </c>
+      <c r="T766" s="9">
+        <f>IF(H766="","",IF(MAX(H766,I766)&lt;TODAY(),"Terminé",IF(H766&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="9" t="inlineStr">
+        <is>
+          <t>EHFCL-2627-005</t>
+        </is>
+      </c>
+      <c r="B767" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C767" s="9" t="inlineStr">
+        <is>
+          <t>EHF Champions League</t>
+        </is>
+      </c>
+      <c r="D767" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E767" s="9" t="inlineStr">
+        <is>
+          <t>Phase de groupes</t>
+        </is>
+      </c>
+      <c r="F767" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G767" s="9" t="inlineStr">
+        <is>
+          <t>Ligue des champions EHF – Journée 5</t>
+        </is>
+      </c>
+      <c r="H767" s="10" t="n">
+        <v>46316</v>
+      </c>
+      <c r="I767" s="10" t="n">
+        <v>46317</v>
+      </c>
+      <c r="J767" s="11" t="n"/>
+      <c r="K767" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L767" s="9" t="n"/>
+      <c r="M767" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N767" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O767" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P767" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q767" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R767" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S767" s="9" t="inlineStr">
+        <is>
+          <t>Repère GP5 du calendrier LNH</t>
+        </is>
+      </c>
+      <c r="T767" s="9">
+        <f>IF(H767="","",IF(MAX(H767,I767)&lt;TODAY(),"Terminé",IF(H767&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="9" t="inlineStr">
+        <is>
+          <t>EHFCL-2627-006</t>
+        </is>
+      </c>
+      <c r="B768" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C768" s="9" t="inlineStr">
+        <is>
+          <t>EHF Champions League</t>
+        </is>
+      </c>
+      <c r="D768" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E768" s="9" t="inlineStr">
+        <is>
+          <t>Phase de groupes</t>
+        </is>
+      </c>
+      <c r="F768" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G768" s="9" t="inlineStr">
+        <is>
+          <t>Ligue des champions EHF – Journée 6</t>
+        </is>
+      </c>
+      <c r="H768" s="10" t="n">
+        <v>46323</v>
+      </c>
+      <c r="I768" s="10" t="n">
+        <v>46324</v>
+      </c>
+      <c r="J768" s="11" t="n"/>
+      <c r="K768" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L768" s="9" t="n"/>
+      <c r="M768" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N768" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O768" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P768" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q768" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R768" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S768" s="9" t="inlineStr">
+        <is>
+          <t>Repère GP6 du calendrier LNH</t>
+        </is>
+      </c>
+      <c r="T768" s="9">
+        <f>IF(H768="","",IF(MAX(H768,I768)&lt;TODAY(),"Terminé",IF(H768&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="9" t="inlineStr">
+        <is>
+          <t>EHFCL-2627-007</t>
+        </is>
+      </c>
+      <c r="B769" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C769" s="9" t="inlineStr">
+        <is>
+          <t>EHF Champions League</t>
+        </is>
+      </c>
+      <c r="D769" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E769" s="9" t="inlineStr">
+        <is>
+          <t>Phase de groupes</t>
+        </is>
+      </c>
+      <c r="F769" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G769" s="9" t="inlineStr">
+        <is>
+          <t>Ligue des champions EHF – Journée 7</t>
+        </is>
+      </c>
+      <c r="H769" s="10" t="n">
+        <v>46344</v>
+      </c>
+      <c r="I769" s="10" t="n">
+        <v>46345</v>
+      </c>
+      <c r="J769" s="11" t="n"/>
+      <c r="K769" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L769" s="9" t="n"/>
+      <c r="M769" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N769" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O769" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P769" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q769" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R769" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S769" s="9" t="inlineStr">
+        <is>
+          <t>Repère MR1 du calendrier LNH</t>
+        </is>
+      </c>
+      <c r="T769" s="9">
+        <f>IF(H769="","",IF(MAX(H769,I769)&lt;TODAY(),"Terminé",IF(H769&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="9" t="inlineStr">
+        <is>
+          <t>EHFCL-2627-008</t>
+        </is>
+      </c>
+      <c r="B770" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C770" s="9" t="inlineStr">
+        <is>
+          <t>EHF Champions League</t>
+        </is>
+      </c>
+      <c r="D770" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E770" s="9" t="inlineStr">
+        <is>
+          <t>Phase de groupes</t>
+        </is>
+      </c>
+      <c r="F770" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G770" s="9" t="inlineStr">
+        <is>
+          <t>Ligue des champions EHF – Journée 8</t>
+        </is>
+      </c>
+      <c r="H770" s="10" t="n">
+        <v>46351</v>
+      </c>
+      <c r="I770" s="10" t="n">
+        <v>46352</v>
+      </c>
+      <c r="J770" s="11" t="n"/>
+      <c r="K770" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L770" s="9" t="n"/>
+      <c r="M770" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N770" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O770" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P770" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q770" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R770" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S770" s="9" t="inlineStr">
+        <is>
+          <t>Repère MR2 du calendrier LNH</t>
+        </is>
+      </c>
+      <c r="T770" s="9">
+        <f>IF(H770="","",IF(MAX(H770,I770)&lt;TODAY(),"Terminé",IF(H770&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="9" t="inlineStr">
+        <is>
+          <t>EHFCL-2627-009</t>
+        </is>
+      </c>
+      <c r="B771" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C771" s="9" t="inlineStr">
+        <is>
+          <t>EHF Champions League</t>
+        </is>
+      </c>
+      <c r="D771" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E771" s="9" t="inlineStr">
+        <is>
+          <t>Phase de groupes</t>
+        </is>
+      </c>
+      <c r="F771" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G771" s="9" t="inlineStr">
+        <is>
+          <t>Ligue des champions EHF – Journée 9</t>
+        </is>
+      </c>
+      <c r="H771" s="10" t="n">
+        <v>46358</v>
+      </c>
+      <c r="I771" s="10" t="n">
+        <v>46359</v>
+      </c>
+      <c r="J771" s="11" t="n"/>
+      <c r="K771" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L771" s="9" t="n"/>
+      <c r="M771" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N771" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O771" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P771" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q771" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R771" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S771" s="9" t="inlineStr">
+        <is>
+          <t>Repère MR3 du calendrier LNH</t>
+        </is>
+      </c>
+      <c r="T771" s="9">
+        <f>IF(H771="","",IF(MAX(H771,I771)&lt;TODAY(),"Terminé",IF(H771&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="9" t="inlineStr">
+        <is>
+          <t>EHFCL-2627-010</t>
+        </is>
+      </c>
+      <c r="B772" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C772" s="9" t="inlineStr">
+        <is>
+          <t>EHF Champions League</t>
+        </is>
+      </c>
+      <c r="D772" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E772" s="9" t="inlineStr">
+        <is>
+          <t>Phase de groupes</t>
+        </is>
+      </c>
+      <c r="F772" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G772" s="9" t="inlineStr">
+        <is>
+          <t>Ligue des champions EHF – Journée 10</t>
+        </is>
+      </c>
+      <c r="H772" s="10" t="n">
+        <v>46365</v>
+      </c>
+      <c r="I772" s="10" t="n">
+        <v>46366</v>
+      </c>
+      <c r="J772" s="11" t="n"/>
+      <c r="K772" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L772" s="9" t="n"/>
+      <c r="M772" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N772" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O772" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P772" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q772" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R772" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S772" s="9" t="inlineStr">
+        <is>
+          <t>Repère MR4 du calendrier LNH</t>
+        </is>
+      </c>
+      <c r="T772" s="9">
+        <f>IF(H772="","",IF(MAX(H772,I772)&lt;TODAY(),"Terminé",IF(H772&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="9" t="inlineStr">
+        <is>
+          <t>EHFCL-2627-011</t>
+        </is>
+      </c>
+      <c r="B773" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C773" s="9" t="inlineStr">
+        <is>
+          <t>EHF Champions League</t>
+        </is>
+      </c>
+      <c r="D773" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E773" s="9" t="inlineStr">
+        <is>
+          <t>Phase de groupes</t>
+        </is>
+      </c>
+      <c r="F773" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="G773" s="9" t="inlineStr">
+        <is>
+          <t>Ligue des champions EHF – Journée 11</t>
+        </is>
+      </c>
+      <c r="H773" s="10" t="n">
+        <v>46428</v>
+      </c>
+      <c r="I773" s="10" t="n">
+        <v>46429</v>
+      </c>
+      <c r="J773" s="11" t="n"/>
+      <c r="K773" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L773" s="9" t="n"/>
+      <c r="M773" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N773" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O773" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P773" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q773" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R773" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S773" s="9" t="inlineStr">
+        <is>
+          <t>Repère MR5 du calendrier LNH</t>
+        </is>
+      </c>
+      <c r="T773" s="9">
+        <f>IF(H773="","",IF(MAX(H773,I773)&lt;TODAY(),"Terminé",IF(H773&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="9" t="inlineStr">
+        <is>
+          <t>EHFCL-2627-012</t>
+        </is>
+      </c>
+      <c r="B774" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C774" s="9" t="inlineStr">
+        <is>
+          <t>EHF Champions League</t>
+        </is>
+      </c>
+      <c r="D774" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E774" s="9" t="inlineStr">
+        <is>
+          <t>Phase de groupes</t>
+        </is>
+      </c>
+      <c r="F774" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="G774" s="9" t="inlineStr">
+        <is>
+          <t>Ligue des champions EHF – Journée 12</t>
+        </is>
+      </c>
+      <c r="H774" s="10" t="n">
+        <v>46435</v>
+      </c>
+      <c r="I774" s="10" t="n">
+        <v>46436</v>
+      </c>
+      <c r="J774" s="11" t="n"/>
+      <c r="K774" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L774" s="9" t="n"/>
+      <c r="M774" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N774" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O774" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P774" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q774" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R774" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S774" s="9" t="inlineStr">
+        <is>
+          <t>Repère MR6 du calendrier LNH</t>
+        </is>
+      </c>
+      <c r="T774" s="9">
+        <f>IF(H774="","",IF(MAX(H774,I774)&lt;TODAY(),"Terminé",IF(H774&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="9" t="inlineStr">
+        <is>
+          <t>EHFCL-2627-013</t>
+        </is>
+      </c>
+      <c r="B775" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C775" s="9" t="inlineStr">
+        <is>
+          <t>EHF Champions League</t>
+        </is>
+      </c>
+      <c r="D775" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E775" s="9" t="inlineStr">
+        <is>
+          <t>Phase de groupes</t>
+        </is>
+      </c>
+      <c r="F775" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="G775" s="9" t="inlineStr">
+        <is>
+          <t>Ligue des champions EHF – Journée 13</t>
+        </is>
+      </c>
+      <c r="H775" s="10" t="n">
+        <v>46442</v>
+      </c>
+      <c r="I775" s="10" t="n">
+        <v>46443</v>
+      </c>
+      <c r="J775" s="11" t="n"/>
+      <c r="K775" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L775" s="9" t="n"/>
+      <c r="M775" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N775" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O775" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P775" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q775" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R775" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S775" s="9" t="inlineStr">
+        <is>
+          <t>Repère MR7 du calendrier LNH</t>
+        </is>
+      </c>
+      <c r="T775" s="9">
+        <f>IF(H775="","",IF(MAX(H775,I775)&lt;TODAY(),"Terminé",IF(H775&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="9" t="inlineStr">
+        <is>
+          <t>EHFCL-2627-014</t>
+        </is>
+      </c>
+      <c r="B776" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C776" s="9" t="inlineStr">
+        <is>
+          <t>EHF Champions League</t>
+        </is>
+      </c>
+      <c r="D776" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E776" s="9" t="inlineStr">
+        <is>
+          <t>Phase de groupes</t>
+        </is>
+      </c>
+      <c r="F776" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="G776" s="9" t="inlineStr">
+        <is>
+          <t>Ligue des champions EHF – Journée 14</t>
+        </is>
+      </c>
+      <c r="H776" s="10" t="n">
+        <v>46449</v>
+      </c>
+      <c r="I776" s="10" t="n">
+        <v>46450</v>
+      </c>
+      <c r="J776" s="11" t="n"/>
+      <c r="K776" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L776" s="9" t="n"/>
+      <c r="M776" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N776" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O776" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P776" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q776" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R776" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S776" s="9" t="inlineStr">
+        <is>
+          <t>Repère MR8 du calendrier LNH</t>
+        </is>
+      </c>
+      <c r="T776" s="9">
+        <f>IF(H776="","",IF(MAX(H776,I776)&lt;TODAY(),"Terminé",IF(H776&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="9" t="inlineStr">
+        <is>
+          <t>EHFCL-2627-015</t>
+        </is>
+      </c>
+      <c r="B777" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C777" s="9" t="inlineStr">
+        <is>
+          <t>EHF Champions League</t>
+        </is>
+      </c>
+      <c r="D777" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E777" s="9" t="inlineStr">
+        <is>
+          <t>Quarts de finale</t>
+        </is>
+      </c>
+      <c r="F777" s="9" t="inlineStr">
+        <is>
+          <t>Aller</t>
+        </is>
+      </c>
+      <c r="G777" s="9" t="inlineStr">
+        <is>
+          <t>Ligue des champions EHF – Quarts de finale (aller)</t>
+        </is>
+      </c>
+      <c r="H777" s="10" t="n">
+        <v>46470</v>
+      </c>
+      <c r="I777" s="10" t="n">
+        <v>46471</v>
+      </c>
+      <c r="J777" s="11" t="n"/>
+      <c r="K777" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L777" s="9" t="n"/>
+      <c r="M777" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N777" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O777" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P777" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q777" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R777" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S777" s="9" t="inlineStr">
+        <is>
+          <t>Libellé QF du calendrier LNH</t>
+        </is>
+      </c>
+      <c r="T777" s="9">
+        <f>IF(H777="","",IF(MAX(H777,I777)&lt;TODAY(),"Terminé",IF(H777&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="9" t="inlineStr">
+        <is>
+          <t>EHFCL-2627-016</t>
+        </is>
+      </c>
+      <c r="B778" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C778" s="9" t="inlineStr">
+        <is>
+          <t>EHF Champions League</t>
+        </is>
+      </c>
+      <c r="D778" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E778" s="9" t="inlineStr">
+        <is>
+          <t>Quarts de finale</t>
+        </is>
+      </c>
+      <c r="F778" s="9" t="inlineStr">
+        <is>
+          <t>Retour</t>
+        </is>
+      </c>
+      <c r="G778" s="9" t="inlineStr">
+        <is>
+          <t>Ligue des champions EHF – Quarts de finale (retour)</t>
+        </is>
+      </c>
+      <c r="H778" s="10" t="n">
+        <v>46477</v>
+      </c>
+      <c r="I778" s="10" t="n">
+        <v>46478</v>
+      </c>
+      <c r="J778" s="11" t="n"/>
+      <c r="K778" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L778" s="9" t="n"/>
+      <c r="M778" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N778" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O778" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P778" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q778" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R778" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S778" s="9" t="inlineStr">
+        <is>
+          <t>Libellé QF du calendrier LNH</t>
+        </is>
+      </c>
+      <c r="T778" s="9">
+        <f>IF(H778="","",IF(MAX(H778,I778)&lt;TODAY(),"Terminé",IF(H778&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="9" t="inlineStr">
+        <is>
+          <t>EHFCL-2627-017</t>
+        </is>
+      </c>
+      <c r="B779" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C779" s="9" t="inlineStr">
+        <is>
+          <t>EHF Champions League</t>
+        </is>
+      </c>
+      <c r="D779" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E779" s="9" t="inlineStr">
+        <is>
+          <t>Final Four</t>
+        </is>
+      </c>
+      <c r="F779" s="9" t="n"/>
+      <c r="G779" s="9" t="inlineStr">
+        <is>
+          <t>Ligue des champions EHF – Final Four</t>
+        </is>
+      </c>
+      <c r="H779" s="10" t="n">
+        <v>46550</v>
+      </c>
+      <c r="I779" s="10" t="n">
+        <v>46551</v>
+      </c>
+      <c r="J779" s="11" t="n"/>
+      <c r="K779" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L779" s="9" t="n"/>
+      <c r="M779" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N779" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O779" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P779" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q779" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R779" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S779" s="9" t="inlineStr">
+        <is>
+          <t>Lieu non précisé dans le calendrier LNH</t>
+        </is>
+      </c>
+      <c r="T779" s="9">
+        <f>IF(H779="","",IF(MAX(H779,I779)&lt;TODAY(),"Terminé",IF(H779&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="9" t="inlineStr">
+        <is>
+          <t>EHFEL-2627-001</t>
+        </is>
+      </c>
+      <c r="B780" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C780" s="9" t="inlineStr">
+        <is>
+          <t>EHF European League</t>
+        </is>
+      </c>
+      <c r="D780" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E780" s="9" t="inlineStr">
+        <is>
+          <t>Phase de groupes</t>
+        </is>
+      </c>
+      <c r="F780" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G780" s="9" t="inlineStr">
+        <is>
+          <t>Ligue européenne EHF – Journée 1</t>
+        </is>
+      </c>
+      <c r="H780" s="10" t="n">
+        <v>46294</v>
+      </c>
+      <c r="I780" s="10" t="n">
+        <v>46294</v>
+      </c>
+      <c r="J780" s="11" t="n"/>
+      <c r="K780" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L780" s="9" t="n"/>
+      <c r="M780" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N780" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O780" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P780" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q780" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R780" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S780" s="9" t="n"/>
+      <c r="T780" s="9">
+        <f>IF(H780="","",IF(MAX(H780,I780)&lt;TODAY(),"Terminé",IF(H780&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="9" t="inlineStr">
+        <is>
+          <t>EHFEL-2627-002</t>
+        </is>
+      </c>
+      <c r="B781" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C781" s="9" t="inlineStr">
+        <is>
+          <t>EHF European League</t>
+        </is>
+      </c>
+      <c r="D781" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E781" s="9" t="inlineStr">
+        <is>
+          <t>Phase de groupes</t>
+        </is>
+      </c>
+      <c r="F781" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G781" s="9" t="inlineStr">
+        <is>
+          <t>Ligue européenne EHF – Journée 2</t>
+        </is>
+      </c>
+      <c r="H781" s="10" t="n">
+        <v>46301</v>
+      </c>
+      <c r="I781" s="10" t="n">
+        <v>46301</v>
+      </c>
+      <c r="J781" s="11" t="n"/>
+      <c r="K781" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L781" s="9" t="n"/>
+      <c r="M781" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N781" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O781" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P781" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q781" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R781" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S781" s="9" t="n"/>
+      <c r="T781" s="9">
+        <f>IF(H781="","",IF(MAX(H781,I781)&lt;TODAY(),"Terminé",IF(H781&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="9" t="inlineStr">
+        <is>
+          <t>EHFEL-2627-003</t>
+        </is>
+      </c>
+      <c r="B782" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C782" s="9" t="inlineStr">
+        <is>
+          <t>EHF European League</t>
+        </is>
+      </c>
+      <c r="D782" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E782" s="9" t="inlineStr">
+        <is>
+          <t>Phase de groupes</t>
+        </is>
+      </c>
+      <c r="F782" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G782" s="9" t="inlineStr">
+        <is>
+          <t>Ligue européenne EHF – Journée 3</t>
+        </is>
+      </c>
+      <c r="H782" s="10" t="n">
+        <v>46308</v>
+      </c>
+      <c r="I782" s="10" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J782" s="11" t="n"/>
+      <c r="K782" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L782" s="9" t="n"/>
+      <c r="M782" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N782" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O782" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P782" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q782" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R782" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S782" s="9" t="n"/>
+      <c r="T782" s="9">
+        <f>IF(H782="","",IF(MAX(H782,I782)&lt;TODAY(),"Terminé",IF(H782&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="9" t="inlineStr">
+        <is>
+          <t>EHFEL-2627-004</t>
+        </is>
+      </c>
+      <c r="B783" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C783" s="9" t="inlineStr">
+        <is>
+          <t>EHF European League</t>
+        </is>
+      </c>
+      <c r="D783" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E783" s="9" t="inlineStr">
+        <is>
+          <t>Phase de groupes</t>
+        </is>
+      </c>
+      <c r="F783" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G783" s="9" t="inlineStr">
+        <is>
+          <t>Ligue européenne EHF – Journée 4</t>
+        </is>
+      </c>
+      <c r="H783" s="10" t="n">
+        <v>46343</v>
+      </c>
+      <c r="I783" s="10" t="n">
+        <v>46343</v>
+      </c>
+      <c r="J783" s="11" t="n"/>
+      <c r="K783" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L783" s="9" t="n"/>
+      <c r="M783" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N783" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O783" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P783" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q783" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R783" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S783" s="9" t="n"/>
+      <c r="T783" s="9">
+        <f>IF(H783="","",IF(MAX(H783,I783)&lt;TODAY(),"Terminé",IF(H783&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="9" t="inlineStr">
+        <is>
+          <t>EHFEL-2627-005</t>
+        </is>
+      </c>
+      <c r="B784" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C784" s="9" t="inlineStr">
+        <is>
+          <t>EHF European League</t>
+        </is>
+      </c>
+      <c r="D784" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E784" s="9" t="inlineStr">
+        <is>
+          <t>Phase de groupes</t>
+        </is>
+      </c>
+      <c r="F784" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G784" s="9" t="inlineStr">
+        <is>
+          <t>Ligue européenne EHF – Journée 5</t>
+        </is>
+      </c>
+      <c r="H784" s="10" t="n">
+        <v>46350</v>
+      </c>
+      <c r="I784" s="10" t="n">
+        <v>46350</v>
+      </c>
+      <c r="J784" s="11" t="n"/>
+      <c r="K784" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L784" s="9" t="n"/>
+      <c r="M784" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N784" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O784" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P784" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q784" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R784" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S784" s="9" t="n"/>
+      <c r="T784" s="9">
+        <f>IF(H784="","",IF(MAX(H784,I784)&lt;TODAY(),"Terminé",IF(H784&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="9" t="inlineStr">
+        <is>
+          <t>EHFEL-2627-006</t>
+        </is>
+      </c>
+      <c r="B785" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C785" s="9" t="inlineStr">
+        <is>
+          <t>EHF European League</t>
+        </is>
+      </c>
+      <c r="D785" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E785" s="9" t="inlineStr">
+        <is>
+          <t>Phase de groupes</t>
+        </is>
+      </c>
+      <c r="F785" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G785" s="9" t="inlineStr">
+        <is>
+          <t>Ligue européenne EHF – Journée 6</t>
+        </is>
+      </c>
+      <c r="H785" s="10" t="n">
+        <v>46357</v>
+      </c>
+      <c r="I785" s="10" t="n">
+        <v>46357</v>
+      </c>
+      <c r="J785" s="11" t="n"/>
+      <c r="K785" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L785" s="9" t="n"/>
+      <c r="M785" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N785" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O785" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P785" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q785" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R785" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S785" s="9" t="n"/>
+      <c r="T785" s="9">
+        <f>IF(H785="","",IF(MAX(H785,I785)&lt;TODAY(),"Terminé",IF(H785&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="9" t="inlineStr">
+        <is>
+          <t>EHFEL-2627-007</t>
+        </is>
+      </c>
+      <c r="B786" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C786" s="9" t="inlineStr">
+        <is>
+          <t>EHF European League</t>
+        </is>
+      </c>
+      <c r="D786" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E786" s="9" t="inlineStr">
+        <is>
+          <t>Tour principal</t>
+        </is>
+      </c>
+      <c r="F786" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G786" s="9" t="inlineStr">
+        <is>
+          <t>Ligue européenne EHF – Tour principal, journée 1</t>
+        </is>
+      </c>
+      <c r="H786" s="10" t="n">
+        <v>46427</v>
+      </c>
+      <c r="I786" s="10" t="n">
+        <v>46427</v>
+      </c>
+      <c r="J786" s="11" t="n"/>
+      <c r="K786" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L786" s="9" t="n"/>
+      <c r="M786" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N786" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O786" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P786" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q786" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R786" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S786" s="9" t="inlineStr">
+        <is>
+          <t>Libellé PO du calendrier LNH</t>
+        </is>
+      </c>
+      <c r="T786" s="9">
+        <f>IF(H786="","",IF(MAX(H786,I786)&lt;TODAY(),"Terminé",IF(H786&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="9" t="inlineStr">
+        <is>
+          <t>EHFEL-2627-008</t>
+        </is>
+      </c>
+      <c r="B787" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C787" s="9" t="inlineStr">
+        <is>
+          <t>EHF European League</t>
+        </is>
+      </c>
+      <c r="D787" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E787" s="9" t="inlineStr">
+        <is>
+          <t>Tour principal</t>
+        </is>
+      </c>
+      <c r="F787" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G787" s="9" t="inlineStr">
+        <is>
+          <t>Ligue européenne EHF – Tour principal, journée 2</t>
+        </is>
+      </c>
+      <c r="H787" s="10" t="n">
+        <v>46434</v>
+      </c>
+      <c r="I787" s="10" t="n">
+        <v>46434</v>
+      </c>
+      <c r="J787" s="11" t="n"/>
+      <c r="K787" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L787" s="9" t="n"/>
+      <c r="M787" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N787" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O787" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P787" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q787" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R787" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S787" s="9" t="inlineStr">
+        <is>
+          <t>Libellé PO du calendrier LNH</t>
+        </is>
+      </c>
+      <c r="T787" s="9">
+        <f>IF(H787="","",IF(MAX(H787,I787)&lt;TODAY(),"Terminé",IF(H787&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="9" t="inlineStr">
+        <is>
+          <t>EHFEL-2627-009</t>
+        </is>
+      </c>
+      <c r="B788" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C788" s="9" t="inlineStr">
+        <is>
+          <t>EHF European League</t>
+        </is>
+      </c>
+      <c r="D788" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E788" s="9" t="inlineStr">
+        <is>
+          <t>Tour principal</t>
+        </is>
+      </c>
+      <c r="F788" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G788" s="9" t="inlineStr">
+        <is>
+          <t>Ligue européenne EHF – Tour principal, journée 3</t>
+        </is>
+      </c>
+      <c r="H788" s="10" t="n">
+        <v>46441</v>
+      </c>
+      <c r="I788" s="10" t="n">
+        <v>46441</v>
+      </c>
+      <c r="J788" s="11" t="n"/>
+      <c r="K788" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L788" s="9" t="n"/>
+      <c r="M788" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N788" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O788" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P788" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q788" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R788" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S788" s="9" t="inlineStr">
+        <is>
+          <t>Libellé PO du calendrier LNH</t>
+        </is>
+      </c>
+      <c r="T788" s="9">
+        <f>IF(H788="","",IF(MAX(H788,I788)&lt;TODAY(),"Terminé",IF(H788&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="9" t="inlineStr">
+        <is>
+          <t>EHFEL-2627-010</t>
+        </is>
+      </c>
+      <c r="B789" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C789" s="9" t="inlineStr">
+        <is>
+          <t>EHF European League</t>
+        </is>
+      </c>
+      <c r="D789" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E789" s="9" t="inlineStr">
+        <is>
+          <t>Tour principal</t>
+        </is>
+      </c>
+      <c r="F789" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G789" s="9" t="inlineStr">
+        <is>
+          <t>Ligue européenne EHF – Tour principal, journée 4</t>
+        </is>
+      </c>
+      <c r="H789" s="10" t="n">
+        <v>46448</v>
+      </c>
+      <c r="I789" s="10" t="n">
+        <v>46448</v>
+      </c>
+      <c r="J789" s="11" t="n"/>
+      <c r="K789" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L789" s="9" t="n"/>
+      <c r="M789" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N789" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O789" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P789" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q789" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R789" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S789" s="9" t="inlineStr">
+        <is>
+          <t>Libellé PO du calendrier LNH</t>
+        </is>
+      </c>
+      <c r="T789" s="9">
+        <f>IF(H789="","",IF(MAX(H789,I789)&lt;TODAY(),"Terminé",IF(H789&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="9" t="inlineStr">
+        <is>
+          <t>EHFEL-2627-011</t>
+        </is>
+      </c>
+      <c r="B790" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C790" s="9" t="inlineStr">
+        <is>
+          <t>EHF European League</t>
+        </is>
+      </c>
+      <c r="D790" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E790" s="9" t="inlineStr">
+        <is>
+          <t>Huitièmes de finale</t>
+        </is>
+      </c>
+      <c r="F790" s="9" t="inlineStr">
+        <is>
+          <t>Aller</t>
+        </is>
+      </c>
+      <c r="G790" s="9" t="inlineStr">
+        <is>
+          <t>Ligue européenne EHF – Huitièmes de finale (aller)</t>
+        </is>
+      </c>
+      <c r="H790" s="10" t="n">
+        <v>46469</v>
+      </c>
+      <c r="I790" s="10" t="n">
+        <v>46469</v>
+      </c>
+      <c r="J790" s="11" t="n"/>
+      <c r="K790" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L790" s="9" t="n"/>
+      <c r="M790" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N790" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O790" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P790" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q790" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R790" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S790" s="9" t="n"/>
+      <c r="T790" s="9">
+        <f>IF(H790="","",IF(MAX(H790,I790)&lt;TODAY(),"Terminé",IF(H790&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="9" t="inlineStr">
+        <is>
+          <t>EHFEL-2627-012</t>
+        </is>
+      </c>
+      <c r="B791" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C791" s="9" t="inlineStr">
+        <is>
+          <t>EHF European League</t>
+        </is>
+      </c>
+      <c r="D791" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E791" s="9" t="inlineStr">
+        <is>
+          <t>Huitièmes de finale</t>
+        </is>
+      </c>
+      <c r="F791" s="9" t="inlineStr">
+        <is>
+          <t>Retour</t>
+        </is>
+      </c>
+      <c r="G791" s="9" t="inlineStr">
+        <is>
+          <t>Ligue européenne EHF – Huitièmes de finale (retour)</t>
+        </is>
+      </c>
+      <c r="H791" s="10" t="n">
+        <v>46476</v>
+      </c>
+      <c r="I791" s="10" t="n">
+        <v>46476</v>
+      </c>
+      <c r="J791" s="11" t="n"/>
+      <c r="K791" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L791" s="9" t="n"/>
+      <c r="M791" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N791" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O791" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P791" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q791" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R791" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S791" s="9" t="n"/>
+      <c r="T791" s="9">
+        <f>IF(H791="","",IF(MAX(H791,I791)&lt;TODAY(),"Terminé",IF(H791&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="9" t="inlineStr">
+        <is>
+          <t>EHFEL-2627-013</t>
+        </is>
+      </c>
+      <c r="B792" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C792" s="9" t="inlineStr">
+        <is>
+          <t>EHF European League</t>
+        </is>
+      </c>
+      <c r="D792" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E792" s="9" t="inlineStr">
+        <is>
+          <t>Quarts de finale</t>
+        </is>
+      </c>
+      <c r="F792" s="9" t="inlineStr">
+        <is>
+          <t>Aller</t>
+        </is>
+      </c>
+      <c r="G792" s="9" t="inlineStr">
+        <is>
+          <t>Ligue européenne EHF – Quarts de finale (aller)</t>
+        </is>
+      </c>
+      <c r="H792" s="10" t="n">
+        <v>46497</v>
+      </c>
+      <c r="I792" s="10" t="n">
+        <v>46498</v>
+      </c>
+      <c r="J792" s="11" t="n"/>
+      <c r="K792" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L792" s="9" t="n"/>
+      <c r="M792" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N792" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O792" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P792" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q792" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R792" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S792" s="9" t="n"/>
+      <c r="T792" s="9">
+        <f>IF(H792="","",IF(MAX(H792,I792)&lt;TODAY(),"Terminé",IF(H792&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="9" t="inlineStr">
+        <is>
+          <t>EHFEL-2627-014</t>
+        </is>
+      </c>
+      <c r="B793" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C793" s="9" t="inlineStr">
+        <is>
+          <t>EHF European League</t>
+        </is>
+      </c>
+      <c r="D793" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E793" s="9" t="inlineStr">
+        <is>
+          <t>Quarts de finale</t>
+        </is>
+      </c>
+      <c r="F793" s="9" t="inlineStr">
+        <is>
+          <t>Retour</t>
+        </is>
+      </c>
+      <c r="G793" s="9" t="inlineStr">
+        <is>
+          <t>Ligue européenne EHF – Quarts de finale (retour)</t>
+        </is>
+      </c>
+      <c r="H793" s="10" t="n">
+        <v>46504</v>
+      </c>
+      <c r="I793" s="10" t="n">
+        <v>46505</v>
+      </c>
+      <c r="J793" s="11" t="n"/>
+      <c r="K793" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L793" s="9" t="n"/>
+      <c r="M793" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N793" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O793" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P793" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q793" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R793" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S793" s="9" t="n"/>
+      <c r="T793" s="9">
+        <f>IF(H793="","",IF(MAX(H793,I793)&lt;TODAY(),"Terminé",IF(H793&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="9" t="inlineStr">
+        <is>
+          <t>EHFEL-2627-015</t>
+        </is>
+      </c>
+      <c r="B794" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C794" s="9" t="inlineStr">
+        <is>
+          <t>EHF European League</t>
+        </is>
+      </c>
+      <c r="D794" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E794" s="9" t="inlineStr">
+        <is>
+          <t>Final Four</t>
+        </is>
+      </c>
+      <c r="F794" s="9" t="n"/>
+      <c r="G794" s="9" t="inlineStr">
+        <is>
+          <t>Ligue européenne EHF – Final Four</t>
+        </is>
+      </c>
+      <c r="H794" s="10" t="n">
+        <v>46529</v>
+      </c>
+      <c r="I794" s="10" t="n">
+        <v>46530</v>
+      </c>
+      <c r="J794" s="11" t="n"/>
+      <c r="K794" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L794" s="9" t="n"/>
+      <c r="M794" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N794" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O794" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P794" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q794" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R794" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S794" s="9" t="inlineStr">
+        <is>
+          <t>Lieu non précisé dans le calendrier LNH</t>
+        </is>
+      </c>
+      <c r="T794" s="9">
+        <f>IF(H794="","",IF(MAX(H794,I794)&lt;TODAY(),"Terminé",IF(H794&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="9" t="inlineStr">
+        <is>
+          <t>MCH-2627-001</t>
+        </is>
+      </c>
+      <c r="B795" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C795" s="9" t="inlineStr">
+        <is>
+          <t>Championnat du monde de handball</t>
+        </is>
+      </c>
+      <c r="D795" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E795" s="9" t="inlineStr">
+        <is>
+          <t>Phase finale</t>
+        </is>
+      </c>
+      <c r="F795" s="9" t="n"/>
+      <c r="G795" s="9" t="inlineStr">
+        <is>
+          <t>Championnat du monde masculin 2027</t>
+        </is>
+      </c>
+      <c r="H795" s="10" t="n">
+        <v>46400</v>
+      </c>
+      <c r="I795" s="10" t="n">
+        <v>46418</v>
+      </c>
+      <c r="J795" s="11" t="n"/>
+      <c r="K795" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L795" s="9" t="inlineStr">
+        <is>
+          <t>Allemagne</t>
+        </is>
+      </c>
+      <c r="M795" s="9" t="inlineStr">
+        <is>
+          <t>Allemagne</t>
+        </is>
+      </c>
+      <c r="N795" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O795" s="9" t="inlineStr">
+        <is>
+          <t>Officiel</t>
+        </is>
+      </c>
+      <c r="P795" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q795" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R795" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S795" s="9" t="inlineStr">
+        <is>
+          <t>Dates indiquées sur le calendrier LNH (MWCH 13.-31.01.2027 GER)</t>
+        </is>
+      </c>
+      <c r="T795" s="9">
+        <f>IF(H795="","",IF(MAX(H795,I795)&lt;TODAY(),"Terminé",IF(H795&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="9" t="inlineStr">
+        <is>
+          <t>QEH-2627-001</t>
+        </is>
+      </c>
+      <c r="B796" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C796" s="9" t="inlineStr">
+        <is>
+          <t>Qualifications Euro de handball</t>
+        </is>
+      </c>
+      <c r="D796" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E796" s="9" t="inlineStr">
+        <is>
+          <t>Journées 1 et 2</t>
+        </is>
+      </c>
+      <c r="F796" s="9" t="n"/>
+      <c r="G796" s="9" t="inlineStr">
+        <is>
+          <t>Qualifications Euro 2028 – Journées 1 et 2</t>
+        </is>
+      </c>
+      <c r="H796" s="10" t="n">
+        <v>46328</v>
+      </c>
+      <c r="I796" s="10" t="n">
+        <v>46334</v>
+      </c>
+      <c r="J796" s="11" t="n"/>
+      <c r="K796" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L796" s="9" t="n"/>
+      <c r="M796" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N796" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O796" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P796" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q796" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R796" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S796" s="9" t="inlineStr">
+        <is>
+          <t>Fenêtre internationale (NTW)</t>
+        </is>
+      </c>
+      <c r="T796" s="9">
+        <f>IF(H796="","",IF(MAX(H796,I796)&lt;TODAY(),"Terminé",IF(H796&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="9" t="inlineStr">
+        <is>
+          <t>QEH-2627-002</t>
+        </is>
+      </c>
+      <c r="B797" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C797" s="9" t="inlineStr">
+        <is>
+          <t>Qualifications Euro de handball</t>
+        </is>
+      </c>
+      <c r="D797" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E797" s="9" t="inlineStr">
+        <is>
+          <t>Journées 3 et 4</t>
+        </is>
+      </c>
+      <c r="F797" s="9" t="n"/>
+      <c r="G797" s="9" t="inlineStr">
+        <is>
+          <t>Qualifications Euro 2028 – Journées 3 et 4</t>
+        </is>
+      </c>
+      <c r="H797" s="10" t="n">
+        <v>46454</v>
+      </c>
+      <c r="I797" s="10" t="n">
+        <v>46460</v>
+      </c>
+      <c r="J797" s="11" t="n"/>
+      <c r="K797" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L797" s="9" t="n"/>
+      <c r="M797" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N797" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O797" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P797" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q797" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R797" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S797" s="9" t="inlineStr">
+        <is>
+          <t>Fenêtre internationale (NTW)</t>
+        </is>
+      </c>
+      <c r="T797" s="9">
+        <f>IF(H797="","",IF(MAX(H797,I797)&lt;TODAY(),"Terminé",IF(H797&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="9" t="inlineStr">
+        <is>
+          <t>QEH-2627-003</t>
+        </is>
+      </c>
+      <c r="B798" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C798" s="9" t="inlineStr">
+        <is>
+          <t>Qualifications Euro de handball</t>
+        </is>
+      </c>
+      <c r="D798" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E798" s="9" t="inlineStr">
+        <is>
+          <t>Journées 5 et 6</t>
+        </is>
+      </c>
+      <c r="F798" s="9" t="n"/>
+      <c r="G798" s="9" t="inlineStr">
+        <is>
+          <t>Qualifications Euro 2028 – Journées 5 et 6</t>
+        </is>
+      </c>
+      <c r="H798" s="10" t="n">
+        <v>46510</v>
+      </c>
+      <c r="I798" s="10" t="n">
+        <v>46516</v>
+      </c>
+      <c r="J798" s="11" t="n"/>
+      <c r="K798" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L798" s="9" t="n"/>
+      <c r="M798" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N798" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O798" s="9" t="inlineStr">
+        <is>
+          <t>Provisoire</t>
+        </is>
+      </c>
+      <c r="P798" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q798" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R798" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S798" s="9" t="inlineStr">
+        <is>
+          <t>Fenêtre internationale (NTW)</t>
+        </is>
+      </c>
+      <c r="T798" s="9">
+        <f>IF(H798="","",IF(MAX(H798,I798)&lt;TODAY(),"Terminé",IF(H798&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="9" t="inlineStr">
+        <is>
+          <t>QEH-2627-004</t>
+        </is>
+      </c>
+      <c r="B799" s="9" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C799" s="9" t="inlineStr">
+        <is>
+          <t>Qualifications Euro de handball</t>
+        </is>
+      </c>
+      <c r="D799" s="9" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E799" s="9" t="inlineStr">
+        <is>
+          <t>Euro 2030 – Phase 1</t>
+        </is>
+      </c>
+      <c r="F799" s="9" t="n"/>
+      <c r="G799" s="9" t="inlineStr">
+        <is>
+          <t>Qualifications Euro 2030 – Phase 1</t>
+        </is>
+      </c>
+      <c r="H799" s="10" t="n">
+        <v>46391</v>
+      </c>
+      <c r="I799" s="10" t="n">
+        <v>46399</v>
+      </c>
+      <c r="J799" s="11" t="n"/>
+      <c r="K799" s="9" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+      <c r="L799" s="9" t="n"/>
+      <c r="M799" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="N799" s="9" t="inlineStr">
+        <is>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="O799" s="9" t="inlineStr">
+        <is>
+          <t>À confirmer</t>
+        </is>
+      </c>
+      <c r="P799" s="9" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="Q799" s="9" t="inlineStr">
+        <is>
+          <t>Calendrier provisoire LNH 2026-2027 (PDF LNH, février 2026)</t>
+        </is>
+      </c>
+      <c r="R799" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="S799" s="9" t="inlineStr">
+        <is>
+          <t>Période internationale du 04 au 31/01/2027 partagée avec le Mondial ; jours exacts de la phase 1 non précisés</t>
+        </is>
+      </c>
+      <c r="T799" s="9">
+        <f>IF(H799="","",IF(MAX(H799,I799)&lt;TODAY(),"Terminé",IF(H799&lt;=TODAY(),"En cours","À venir")))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T752"/>
-  <conditionalFormatting sqref="A2:T1252">
+  <autoFilter ref="A1:T799"/>
+  <conditionalFormatting sqref="A2:T1299">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$T2="Terminé"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O1252">
+  <conditionalFormatting sqref="O2:O1299">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>$O2="Provisoire"</formula>
     </cfRule>
@@ -65231,28 +69148,28 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="8">
-    <dataValidation sqref="B2:B1252" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur non autorisée" error="Choisir une valeur de la liste (onglet Référentiels)." type="list">
+    <dataValidation sqref="B2:B1299" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur non autorisée" error="Choisir une valeur de la liste (onglet Référentiels)." type="list">
       <formula1>='Référentiels'!$H$2:$H$30</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C1252" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur non autorisée" error="Choisir une valeur de la liste (onglet Référentiels)." type="list">
-      <formula1>='Référentiels'!$C$2:$C$40</formula1>
+    <dataValidation sqref="C2:C1299" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur non autorisée" error="Choisir une valeur de la liste (onglet Référentiels)." type="list">
+      <formula1>='Référentiels'!$C$2:$C$60</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O1252" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur non autorisée" error="Choisir une valeur de la liste (onglet Référentiels)." type="list">
+    <dataValidation sqref="O2:O1299" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur non autorisée" error="Choisir une valeur de la liste (onglet Référentiels)." type="list">
       <formula1>='Référentiels'!$J$2:$J$10</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N1252" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur non autorisée" error="Choisir une valeur de la liste (onglet Référentiels)." type="list">
+    <dataValidation sqref="N2:N1299" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur non autorisée" error="Choisir une valeur de la liste (onglet Référentiels)." type="list">
       <formula1>='Référentiels'!$K$2:$K$10</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P1252" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur non autorisée" error="Choisir une valeur de la liste (onglet Référentiels)." type="list">
+    <dataValidation sqref="P2:P1299" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur non autorisée" error="Choisir une valeur de la liste (onglet Référentiels)." type="list">
       <formula1>='Référentiels'!$L$2:$L$5</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H1252" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Date attendue" error="Saisir une date au format JJ/MM/AAAA." type="date" operator="greaterThan">
+    <dataValidation sqref="H2:H1299" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Date attendue" error="Saisir une date au format JJ/MM/AAAA." type="date" operator="greaterThan">
       <formula1>DATE(2020,1,1)</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I1252" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Date attendue" error="Saisir une date au format JJ/MM/AAAA." type="date" operator="greaterThan">
+    <dataValidation sqref="I2:I1299" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Date attendue" error="Saisir une date au format JJ/MM/AAAA." type="date" operator="greaterThan">
       <formula1>DATE(2020,1,1)</formula1>
     </dataValidation>
-    <dataValidation sqref="R2:R1252" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Date attendue" error="Saisir une date au format JJ/MM/AAAA." type="date" operator="greaterThan">
+    <dataValidation sqref="R2:R1299" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Date attendue" error="Saisir une date au format JJ/MM/AAAA." type="date" operator="greaterThan">
       <formula1>DATE(2020,1,1)</formula1>
     </dataValidation>
   </dataValidations>
@@ -65266,7 +69183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -65844,7 +69761,7 @@
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>Marmara SpikeLigue</t>
+          <t>Alterna Volstar</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
@@ -66342,13 +70259,258 @@
       </c>
     </row>
     <row r="27">
-      <c r="C27" s="15" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>EHFCL</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>EHF Champions League</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>1 ligne par journée ou par tour</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>https://www.eurohandball.com</t>
+        </is>
+      </c>
+      <c r="F27" s="13">
+        <f>COUNTIF('Épreuves'!$C$2:$C$5000,C27)</f>
+        <v/>
+      </c>
+      <c r="G27" s="14">
+        <f>IFERROR(1/(1/_xlfn.MINIFS('Épreuves'!$H$2:$H$5000,'Épreuves'!$C$2:$C$5000,C27,'Épreuves'!$H$2:$H$5000,"&gt;="&amp;TODAY())),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>EHFEL</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>EHF European League</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>1 ligne par journée ou par tour</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>https://www.eurohandball.com</t>
+        </is>
+      </c>
+      <c r="F28" s="13">
+        <f>COUNTIF('Épreuves'!$C$2:$C$5000,C28)</f>
+        <v/>
+      </c>
+      <c r="G28" s="14">
+        <f>IFERROR(1/(1/_xlfn.MINIFS('Épreuves'!$H$2:$H$5000,'Épreuves'!$C$2:$C$5000,C28,'Épreuves'!$H$2:$H$5000,"&gt;="&amp;TODAY())),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>CDFH</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Coupe de France de handball</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>1 ligne par tour</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>https://www.ffhandball.fr</t>
+        </is>
+      </c>
+      <c r="F29" s="13">
+        <f>COUNTIF('Épreuves'!$C$2:$C$5000,C29)</f>
+        <v/>
+      </c>
+      <c r="G29" s="14">
+        <f>IFERROR(1/(1/_xlfn.MINIFS('Épreuves'!$H$2:$H$5000,'Épreuves'!$C$2:$C$5000,C29,'Épreuves'!$H$2:$H$5000,"&gt;="&amp;TODAY())),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>TDCH</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Trophée des Champions de handball</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>1 ligne par édition</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>https://www.lnh.fr</t>
+        </is>
+      </c>
+      <c r="F30" s="13">
+        <f>COUNTIF('Épreuves'!$C$2:$C$5000,C30)</f>
+        <v/>
+      </c>
+      <c r="G30" s="14">
+        <f>IFERROR(1/(1/_xlfn.MINIFS('Épreuves'!$H$2:$H$5000,'Épreuves'!$C$2:$C$5000,C30,'Épreuves'!$H$2:$H$5000,"&gt;="&amp;TODAY())),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>IHFSG</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>IHF Super Globe</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>1 ligne par édition</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>https://www.ihf.info</t>
+        </is>
+      </c>
+      <c r="F31" s="13">
+        <f>COUNTIF('Épreuves'!$C$2:$C$5000,C31)</f>
+        <v/>
+      </c>
+      <c r="G31" s="14">
+        <f>IFERROR(1/(1/_xlfn.MINIFS('Épreuves'!$H$2:$H$5000,'Épreuves'!$C$2:$C$5000,C31,'Épreuves'!$H$2:$H$5000,"&gt;="&amp;TODAY())),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>MCH</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Championnat du monde de handball</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>1 ligne par édition</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>https://www.ihf.info</t>
+        </is>
+      </c>
+      <c r="F32" s="13">
+        <f>COUNTIF('Épreuves'!$C$2:$C$5000,C32)</f>
+        <v/>
+      </c>
+      <c r="G32" s="14">
+        <f>IFERROR(1/(1/_xlfn.MINIFS('Épreuves'!$H$2:$H$5000,'Épreuves'!$C$2:$C$5000,C32,'Épreuves'!$H$2:$H$5000,"&gt;="&amp;TODAY())),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>QEH</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>Handball</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>Qualifications Euro de handball</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>1 ligne par fenêtre internationale</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>https://www.eurohandball.com</t>
+        </is>
+      </c>
+      <c r="F33" s="13">
+        <f>COUNTIF('Épreuves'!$C$2:$C$5000,C33)</f>
+        <v/>
+      </c>
+      <c r="G33" s="14">
+        <f>IFERROR(1/(1/_xlfn.MINIFS('Épreuves'!$H$2:$H$5000,'Épreuves'!$C$2:$C$5000,C33,'Épreuves'!$H$2:$H$5000,"&gt;="&amp;TODAY())),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" s="15" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="F27" s="15">
-        <f>SUM(F2:F26)</f>
+      <c r="F34" s="15">
+        <f>SUM(F2:F33)</f>
         <v/>
       </c>
     </row>
